--- a/reports/Debug-snowbowl-20260105/Week Total (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260105/Week Total (Prior Year)_Revenue.xlsx
@@ -55,19 +55,19 @@
     <t>account</t>
   </si>
   <si>
+    <t>T100</t>
+  </si>
+  <si>
+    <t>T101</t>
+  </si>
+  <si>
     <t>T121</t>
   </si>
   <si>
-    <t>T101</t>
+    <t>T257</t>
   </si>
   <si>
     <t>T103</t>
-  </si>
-  <si>
-    <t>T100</t>
-  </si>
-  <si>
-    <t>T257</t>
   </si>
   <si>
     <t>department</t>
@@ -496,26 +496,26 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="2">
-        <v>40604.44</v>
+        <v>15800.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="2">
-        <v>94843.00</v>
+        <v>275625.21</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -529,7 +529,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="2">
-        <v>495290.06</v>
+        <v>1965.78</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -543,7 +543,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>10121.31</v>
+        <v>9226.19</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -557,7 +557,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>709055.93</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -571,7 +571,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2">
-        <v>21.38</v>
+        <v>4199.65</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -583,7 +583,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2">
-        <v>103791.42</v>
+        <v>48937.49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -595,7 +595,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2">
-        <v>214421.76</v>
+        <v>126305.01</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -619,7 +619,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="2">
-        <v>103047.61</v>
+        <v>79095.03</v>
       </c>
     </row>
     <row r="12" spans="1:4">
